--- a/Projects/Isaiah Stewart.xlsx
+++ b/Projects/Isaiah Stewart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74D4FAE-D06F-0F4B-A361-45DC8372CA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBB48E9-175F-0842-87B5-492DBC957852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="11" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="49700" yWindow="620" windowWidth="18940" windowHeight="21000" activeTab="7" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -5877,19 +5877,21 @@
     <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -6670,23 +6672,21 @@
     <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
@@ -7391,23 +7391,22 @@
     <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7506,7 +7505,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
@@ -7599,7 +7598,7 @@
       </c>
       <c r="AE2" s="3"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>150</v>
       </c>
@@ -7692,7 +7691,7 @@
       </c>
       <c r="AE3" s="3"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>151</v>
       </c>
